--- a/codigo/tools_cimus/Simple_NK_rutas_activadas_GO.xlsx
+++ b/codigo/tools_cimus/Simple_NK_rutas_activadas_GO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pablo\Desktop\PIA2\piia2-26\codigo\tools_cimus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CA19CEA-3011-471D-B1C6-9578E50BFF38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DC6FE7-7EB3-4BF1-A7B6-F916EF1E587F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
